--- a/etf_holdings/2026-10-20_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-10-20_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:CF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,150 +439,400 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>00403A_異動類型</t>
+          <t>00981A_異動類型</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>00403A_調整方向</t>
+          <t>00981A_調整方向</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_昨日</t>
+          <t>00981A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_今日</t>
+          <t>00981A_股票名稱_今日</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>00403A_權重_昨日</t>
+          <t>00981A_權重_昨日</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>00403A_權重_今日</t>
+          <t>00981A_權重_今日</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>00403A_權重變化</t>
+          <t>00981A_權重變化</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>00403A_股數_昨日</t>
+          <t>00981A_股數_昨日</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>00403A_股數_今日</t>
+          <t>00981A_股數_今日</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>00403A_股數變化</t>
+          <t>00981A_股數變化</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>00991A_異動類型</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>00991A_調整方向</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>00991A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>00991A_權重_今日</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>00991A_權重變化</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>00991A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>00991A_股數_今日</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>00991A_股數變化</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>00982A_異動類型</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>00982A_調整方向</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>00982A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>00982A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>00982A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>00982A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>00982A_權重變化</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>00982A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>00982A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>00982A_股數變化</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
           <t>00985A_異動類型</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>00985A_調整方向</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>00985A_權重_昨日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>00985A_權重_今日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>00985A_權重變化</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>00985A_股數_昨日</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>00985A_股數_今日</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>00985A_股數變化</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>00992A_異動類型</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>00992A_調整方向</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>00992A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>00992A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>00992A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>00992A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>00992A_權重變化</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>00992A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>00992A_股數_今日</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>00992A_股數變化</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>00990A_異動類型</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>00990A_調整方向</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>00990A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>00990A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>00990A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>00990A_權重_今日</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>00990A_權重變化</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>00990A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>00990A_股數_今日</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>00990A_股數變化</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>00407A_異動類型</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>00407A_調整方向</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>00407A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>00407A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>00407A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>00407A_權重_今日</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>00407A_權重變化</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>00407A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>00407A_股數_今日</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>00407A_股數變化</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
         <is>
           <t>00400A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>00400A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>00400A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>00400A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>00400A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>00400A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>00400A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>00400A_股數變化</t>
         </is>
@@ -591,68 +841,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00400A,00403A</t>
+          <t>00407A,00981A,00992A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.57%</t>
-        </is>
-      </c>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>+0.14%</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>75000</v>
-      </c>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>90000</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>15,000</t>
-        </is>
-      </c>
+        <v>4703000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -663,62 +895,148 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>-1.01%</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7185000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4454000</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-2,731,000</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3.00%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>3.79%</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>+0.79%</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>92000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>112000</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>1.09%</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>+0.34%</t>
+        </is>
+      </c>
+      <c r="BT2" t="n">
+        <v>878000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1198000</v>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>320,000</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -726,7 +1044,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00400A,00985A</t>
+          <t>00400A,00991A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -751,96 +1069,146 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>7.08%</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+7.10%</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>378000</v>
+        <v>470000</v>
       </c>
       <c r="W3" t="n">
-        <v>403000</v>
+        <v>482000</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>25,000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.69%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>1.66%</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>+0.97%</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>104000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>252000</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>148,000</t>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>+0.79%</t>
+        </is>
+      </c>
+      <c r="CD3" t="n">
+        <v>92000</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>112000</v>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -848,7 +1216,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00403A,00985A</t>
+          <t>00400A,00981A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -863,86 +1231,50 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>10.86%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>11.30%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1697956</v>
+        <v>12392000</v>
       </c>
       <c r="M4" t="n">
-        <v>1850956</v>
+        <v>12671000</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>153,000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>1.32%</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>+1.18%</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>227036</v>
-      </c>
-      <c r="W4" t="n">
-        <v>392036</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>165,000</t>
-        </is>
-      </c>
+          <t>279,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -953,6 +1285,1106 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>8.71%</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>9.11%</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="CD4" t="n">
+        <v>1094000</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>1131000</v>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>37,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00400A,00985A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>2.35%</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2.74%</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>378000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>403000</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>1.66%</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>+0.97%</t>
+        </is>
+      </c>
+      <c r="CD5" t="n">
+        <v>104000</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>252000</v>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>148,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00985A,00992A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2.87%</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>163000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>165000</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>5.16%</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>4.71%</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>475000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>420000</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-55,000</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00981A,00990A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>5151450</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6351450</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1,200,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="n">
+        <v>967000</v>
+      </c>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00400A,00982A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>6.59%</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>7.03%</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>+0.44%</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>736000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>786000</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>+0.99%</t>
+        </is>
+      </c>
+      <c r="CD8" t="n">
+        <v>445000</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>514000</v>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>69,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00982A,00991A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>+1.51%</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>150000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>170000</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>3.36%</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>251000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>253000</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00981A,00982A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7.58%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7.82%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>+0.24%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>6303000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6343000</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2.64%</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>372000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>374000</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
